--- a/재고확인_신세계푸드_만다린오렌지공문.xlsx
+++ b/재고확인_신세계푸드_만다린오렌지공문.xlsx
@@ -231,7 +231,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -346,6 +346,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -963,7 +965,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>신세계푸드㈜ 은성일 파트너 님</t>
+          <t>신세계푸드㈜ 구매 담당자 님</t>
         </is>
       </c>
       <c r="D8" s="10" t="n"/>
@@ -1119,19 +1121,19 @@
           <t>품목코드</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="29" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="41" t="n"/>
       <c r="F23" s="34" t="inlineStr">
         <is>
           <t>NA106003</t>
         </is>
       </c>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="25" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="40" t="n"/>
+      <c r="I23" s="40" t="n"/>
+      <c r="J23" s="40" t="n"/>
+      <c r="K23" s="41" t="n"/>
       <c r="L23" s="33" t="n"/>
     </row>
     <row r="24" ht="21" customFormat="1" customHeight="1" s="27">
@@ -1140,19 +1142,19 @@
           <t>품목명</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="29" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="41" t="n"/>
       <c r="F24" s="34" t="inlineStr">
         <is>
           <t>화풍 만다린오렌지 3kg (밀감)</t>
         </is>
       </c>
-      <c r="G24" s="25" t="n"/>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="25" t="n"/>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="25" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="40" t="n"/>
+      <c r="I24" s="40" t="n"/>
+      <c r="J24" s="40" t="n"/>
+      <c r="K24" s="41" t="n"/>
       <c r="L24" s="33" t="n"/>
     </row>
     <row r="25" ht="21" customFormat="1" customHeight="1" s="27">
@@ -1161,19 +1163,19 @@
           <t>박스 입수량</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="29" t="n"/>
+      <c r="C25" s="40" t="n"/>
+      <c r="D25" s="40" t="n"/>
+      <c r="E25" s="41" t="n"/>
       <c r="F25" s="34" t="inlineStr">
         <is>
           <t>6ea / 박스</t>
         </is>
       </c>
-      <c r="G25" s="25" t="n"/>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="25" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="40" t="n"/>
+      <c r="I25" s="40" t="n"/>
+      <c r="J25" s="40" t="n"/>
+      <c r="K25" s="41" t="n"/>
       <c r="L25" s="33" t="n"/>
     </row>
     <row r="26" ht="21" customFormat="1" customHeight="1" s="27">
@@ -1182,19 +1184,19 @@
           <t>현 재고 수량</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="29" t="n"/>
-      <c r="E26" s="29" t="n"/>
+      <c r="C26" s="40" t="n"/>
+      <c r="D26" s="40" t="n"/>
+      <c r="E26" s="41" t="n"/>
       <c r="F26" s="34" t="inlineStr">
         <is>
           <t>662ea (110박스 + 낱개 2ea)</t>
         </is>
       </c>
-      <c r="G26" s="25" t="n"/>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="25" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="40" t="n"/>
+      <c r="I26" s="40" t="n"/>
+      <c r="J26" s="40" t="n"/>
+      <c r="K26" s="41" t="n"/>
       <c r="L26" s="33" t="n"/>
     </row>
     <row r="27" ht="21" customFormat="1" customHeight="1" s="27">
@@ -1203,19 +1205,19 @@
           <t>단가</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="29" t="n"/>
+      <c r="C27" s="40" t="n"/>
+      <c r="D27" s="40" t="n"/>
+      <c r="E27" s="41" t="n"/>
       <c r="F27" s="34" t="inlineStr">
         <is>
           <t>8,400원 / ea (신세계푸드 별도 판매가, VAT 별도)</t>
         </is>
       </c>
-      <c r="G27" s="25" t="n"/>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="25" t="n"/>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="25" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="40" t="n"/>
+      <c r="I27" s="40" t="n"/>
+      <c r="J27" s="40" t="n"/>
+      <c r="K27" s="41" t="n"/>
       <c r="L27" s="33" t="n"/>
     </row>
     <row r="28" ht="21" customFormat="1" customHeight="1" s="27">
@@ -1224,19 +1226,19 @@
           <t>재고 금액</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="29" t="n"/>
-      <c r="E28" s="29" t="n"/>
+      <c r="C28" s="40" t="n"/>
+      <c r="D28" s="40" t="n"/>
+      <c r="E28" s="41" t="n"/>
       <c r="F28" s="35" t="inlineStr">
         <is>
           <t>5,560,800원 (662ea × 8,400원, VAT 별도)</t>
         </is>
       </c>
-      <c r="G28" s="25" t="n"/>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="25" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="40" t="n"/>
+      <c r="I28" s="40" t="n"/>
+      <c r="J28" s="40" t="n"/>
+      <c r="K28" s="41" t="n"/>
       <c r="L28" s="33" t="n"/>
     </row>
     <row r="29" ht="21" customFormat="1" customHeight="1" s="27">
@@ -1245,19 +1247,19 @@
           <t>재고 기준일</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="29" t="n"/>
-      <c r="E29" s="29" t="n"/>
+      <c r="C29" s="40" t="n"/>
+      <c r="D29" s="40" t="n"/>
+      <c r="E29" s="41" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
           <t>2026.10.[  ]</t>
         </is>
       </c>
-      <c r="G29" s="25" t="n"/>
-      <c r="H29" s="25" t="n"/>
-      <c r="I29" s="25" t="n"/>
-      <c r="J29" s="25" t="n"/>
-      <c r="K29" s="25" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="40" t="n"/>
+      <c r="I29" s="40" t="n"/>
+      <c r="J29" s="40" t="n"/>
+      <c r="K29" s="41" t="n"/>
       <c r="L29" s="33" t="n"/>
     </row>
     <row r="30" ht="21" customFormat="1" customHeight="1" s="27">
@@ -1266,19 +1268,19 @@
           <t>전산·실재고 일치 여부</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n"/>
-      <c r="D30" s="29" t="n"/>
-      <c r="E30" s="29" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="41" t="n"/>
       <c r="F30" s="35" t="inlineStr">
         <is>
           <t>일치 (전산재고 = 실재고 662ea)</t>
         </is>
       </c>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="25" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="40" t="n"/>
+      <c r="I30" s="40" t="n"/>
+      <c r="J30" s="40" t="n"/>
+      <c r="K30" s="41" t="n"/>
       <c r="L30" s="33" t="n"/>
     </row>
     <row r="31" ht="20.1" customFormat="1" customHeight="1" s="27">
@@ -1525,9 +1527,9 @@
   <mergeCells count="31">
     <mergeCell ref="B50:L50"/>
     <mergeCell ref="F24:K24"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F26:K26"/>
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F26:K26"/>
-    <mergeCell ref="B30:E30"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B33:K33"/>
     <mergeCell ref="B26:E26"/>

--- a/재고확인_신세계푸드_만다린오렌지공문.xlsx
+++ b/재고확인_신세계푸드_만다린오렌지공문.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재고확인 공문" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'재고확인 공문'!$B$1:$L$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'재고확인 공문'!$B$1:$L$94</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -231,7 +231,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -348,6 +348,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -445,7 +446,7 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -486,7 +487,7 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -508,6 +509,90 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6667500" cy="2181225"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3286125" cy="4381500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3286125" cy="4381500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -689,9 +774,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:L52"/>
+  <dimension ref="B2:L68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.25" defaultRowHeight="16.5"/>
   <cols>
     <col width="1.5" customWidth="1" style="20" min="1" max="1"/>
@@ -1252,7 +1337,7 @@
       <c r="E29" s="41" t="n"/>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>2026.10.[  ]</t>
+          <t>2026.10.14</t>
         </is>
       </c>
       <c r="G29" s="40" t="n"/>
@@ -1522,6 +1607,20 @@
       <c r="J52" s="26" t="n"/>
       <c r="K52" s="26" t="n"/>
       <c r="L52" s="26" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>[붙임 1] 전산재고 화면 (창고별 재고현황, 기준일자 2026.10.14 / 이천점 662ea)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="42" t="inlineStr">
+        <is>
+          <t>[붙임 2] 실재고 사진 (이천점 K32 랙, 2PLT / 110box 2ea, 소비기한 28.08.05)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -1559,7 +1658,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.196527777777778" bottom="0" header="0.511811023622047" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="99" fitToHeight="1" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="78" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;R&amp;P/&amp;N</oddFooter>
@@ -1568,6 +1667,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="52" min="0" max="16383" man="1"/>
+  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>